--- a/evals/reports/benchmark.xlsx
+++ b/evals/reports/benchmark.xlsx
@@ -542,20 +542,30 @@
           <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>```sql
+SELECT name, country
+FROM singers
+ORDER BY age DESC;
+```</t>
+        </is>
+      </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.7899999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>0.338</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1412,7 +1422,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) FROM Singers;</t>
+          <t>SELECT COUNT(*) FROM singer;</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1428,7 +1438,7 @@
         <v>0.518</v>
       </c>
       <c r="I32" t="n">
-        <v>4.54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -1449,11 +1459,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS Total_Singers FROM Singers;</t>
+          <t>SELECT COUNT(*) FROM singer;</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="n">
         <v>0.6</v>
@@ -1462,10 +1472,10 @@
         <v>0.4399999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.268</v>
+        <v>0.518</v>
       </c>
       <c r="I33" t="n">
-        <v>7.14</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="34">
@@ -1486,10 +1496,9 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SELECT s.name, c.country
-FROM singers s
-JOIN countries c ON s.country_id = c.id
-ORDER BY s.age DESC;</t>
+          <t>SELECT name, country 
+FROM singer 
+ORDER BY DATE_PART('year', age(birthday)) DESC;</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1505,7 +1514,7 @@
         <v>0.268</v>
       </c>
       <c r="I34" t="n">
-        <v>13.19</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="35">
@@ -1526,9 +1535,9 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SELECT s.name, s.country, s.age
-FROM singers s
-ORDER BY s.age DESC;</t>
+          <t>SELECT s.name, s.country 
+FROM singer s 
+ORDER BY DATEDIFF(CURDATE(), s.birthday) DESC;</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1544,7 +1553,7 @@
         <v>0.268</v>
       </c>
       <c r="I35" t="n">
-        <v>9.449999999999999</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="36">
@@ -1565,9 +1574,9 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SELECT AVG(id), MIN(id), MAX(id)
-FROM singers
-WHERE country='France';</t>
+          <t>SELECT AVG(id), MIN(id), MAX(id) 
+FROM singer 
+WHERE country = 'France';</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1583,7 +1592,7 @@
         <v>0.268</v>
       </c>
       <c r="I36" t="n">
-        <v>9.359999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1604,9 +1613,9 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SELECT AVG(s.id), MIN(s.id), MAX(s.id)
-FROM singers s
-WHERE s.country = 'France';</t>
+          <t>SELECT AVG(id) AS avg_id, MIN(id) AS min_id, MAX(id) AS max_id 
+FROM singer 
+WHERE country='France';</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1622,7 +1631,7 @@
         <v>0.268</v>
       </c>
       <c r="I37" t="n">
-        <v>9.26</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="38">
@@ -1643,10 +1652,10 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SELECT s.name, s.release_year
-FROM singers s
-WHERE s.age = (SELECT MIN(age) FROM singers)
-ORDER BY s.name;</t>
+          <t>SELECT s.name, s.birthday AS birth_year 
+FROM singer s 
+WHERE (SELECT COUNT(*) FROM singer) = 
+       ROW_NUMBER() OVER (ORDER BY s.birthday ASC);</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1662,7 +1671,7 @@
         <v>0.268</v>
       </c>
       <c r="I38" t="n">
-        <v>12.21</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="39">
@@ -1683,12 +1692,10 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SELECT s.name, s.release_year
-FROM singers s
-JOIN songs sgn ON s.id = sgn.singer_id
-ORDER BY s.age ASC;
-SELECT * FROM singers WHERE age = (SELECT MIN(age) FROM singers);
-SELECT name, release_year FROM songs WHERE singer_id IN (SELECT id FROM singers ORDER BY age ASC LIMIT 1);</t>
+          <t>SELECT s.name, 'No year provided' AS release_year
+FROM singer s
+WHERE s.id IN (SELECT MIN(s2.id) 
+               FROM singer s2);</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1704,7 +1711,7 @@
         <v>0.268</v>
       </c>
       <c r="I39" t="n">
-        <v>26.19</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="40">
@@ -1726,8 +1733,8 @@
       <c r="D40" t="inlineStr">
         <is>
           <t>SELECT DISTINCT country 
-FROM artists 
-WHERE birth_year = 2001;</t>
+FROM singer 
+WHERE YEAR(birthday) = 2001;</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1743,7 +1750,7 @@
         <v>0.268</v>
       </c>
       <c r="I40" t="n">
-        <v>7.59</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="41">
@@ -1764,9 +1771,9 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SELECT country 
-FROM singers 
-WHERE birth_year = 2001</t>
+          <t>SELECT DISTINCT country 
+FROM singer 
+WHERE YEAR(birthday) = 2001;</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1782,7 +1789,7 @@
         <v>0.268</v>
       </c>
       <c r="I41" t="n">
-        <v>6.76</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1861,15 +1868,17 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.07899999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0.0338</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1898,7 +1907,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C5" t="n">
         <v>0.6</v>
@@ -1907,10 +1916,10 @@
         <v>0.4399999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.293</v>
+        <v>0.318</v>
       </c>
       <c r="F5" t="n">
-        <v>10.569</v>
+        <v>10.233</v>
       </c>
     </row>
   </sheetData>

--- a/evals/reports/benchmark.xlsx
+++ b/evals/reports/benchmark.xlsx
@@ -623,7 +623,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.49</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>1</v>
@@ -684,7 +684,7 @@
         <v>1</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="N3" s="4" t="n">
         <v>1</v>
@@ -747,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>1</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.3</v>
+        <v>0.61</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>1</v>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3</v>
+        <v>0.61</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>1</v>
@@ -1032,7 +1032,8 @@
         <is>
           <t>SELECT name 
 FROM singer 
-WHERE birthday = (SELECT MAX(birthday) FROM singer)
+ORDER BY birthday DESC 
+LIMIT 1;
 ```</t>
         </is>
       </c>
@@ -1063,7 +1064,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>1</v>
@@ -1126,7 +1127,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="N10" s="2" t="n">
         <v>1</v>
@@ -1189,7 +1190,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>1</v>
@@ -1283,7 +1284,7 @@
         <v>0.74</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.346</v>
+        <v>0.493</v>
       </c>
     </row>
   </sheetData>

--- a/evals/reports/benchmark.xlsx
+++ b/evals/reports/benchmark.xlsx
@@ -62,12 +62,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>groq_llama3</t>
+          <t>gemini_flash</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -590,23 +590,18 @@
           <t>SELECT count(*) FROM singer</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM singer;
-```</t>
-        </is>
-      </c>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -620,25 +615,23 @@
         <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.8999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>groq_llama3</t>
+          <t>gemini_flash</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -651,23 +644,18 @@
           <t>SELECT count(*) FROM singer</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) FROM singer;
-```</t>
-        </is>
-      </c>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
@@ -681,525 +669,2916 @@
         <v>1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0.37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.8999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>gemini_flash</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>gemini_flash</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>What are the names, countries for every singer in descending order of age?</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>gemini_flash</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id of all French singers?</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>gemini_flash</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id for French singers?</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>gemini_flash</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Show the name and the release year of the song by the youngest singer.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>gemini_flash</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>What are the names and release years for all the songs of the youngest singer?</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>gemini_flash</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>What are all distinct countries where singers born in 2001 are from?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like '2001%'</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>gemini_flash</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>What are  the different countries with singers born in 2001?</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>groq_llama3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>How many singers do we have?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>groq_llama3</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>What is the total number of singers?</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>groq_llama3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>SELECT name, country 
 FROM singer 
-ORDER BY birthday ASC;
-```</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>single_agent</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.8999999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>groq_llama3</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>What are the names, countries for every singer in descending order of age?</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>SELECT name, country 
 FROM singer 
-ORDER BY birthday ASC;
-```</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
+ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>single_agent</t>
         </is>
       </c>
-      <c r="J5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.8999999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="J15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>groq_llama3</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>What is the average, minimum, and maximum id of all French singers?</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>SELECT AVG(id), MIN(id), MAX(id) 
 FROM singer 
-WHERE country = 'France';
-```</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+WHERE country = 'France'</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>single_agent</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="5" t="n">
+      <c r="J16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="3" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>groq_llama3</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>What is the average, minimum, and maximum id for French singers?</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>SELECT AVG(id) AS average_id, MIN(id) AS min_id, MAX(id) AS max_id
 FROM singer
-WHERE country = 'France';
-```</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
+WHERE country = 'France'</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>single_agent</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5" t="n">
+      <c r="J17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="3" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>groq_llama3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Show the name and the release year of the song by the youngest singer.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>SELECT name, EXTRACT(YEAR FROM birthday) 
 FROM singer 
 ORDER BY birthday DESC 
-LIMIT 1;
-```</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>single_agent</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="5" t="n">
+      <c r="J18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="3" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>groq_llama3</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>What are the names and release years for all the songs of the youngest singer?</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>SELECT name 
 FROM singer 
 ORDER BY birthday DESC 
-LIMIT 1;
-```</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>single_agent</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" s="5" t="n">
+      <c r="J19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="3" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>groq_llama3</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>What are all distinct countries where singers born in 2001 are from?</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>SELECT DISTINCT country FROM singer WHERE birthday  like '2001%'</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>SELECT DISTINCT country 
 FROM singer 
-WHERE birthday LIKE '2001%';
-```</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+WHERE birthday LIKE '2001%'</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>single_agent</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="2" t="n">
+      <c r="J20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="N10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.8999999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="N20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>groq_llama3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>What are  the different countries with singers born in 2001?</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>SELECT DISTINCT country 
 FROM singer 
-WHERE birthday LIKE '2001%';
-```</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
+WHERE birthday LIKE '2001%'</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>single_agent</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0.8999999999999999</v>
+      <c r="J21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>How many singers do we have?</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>0.9580000000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>What is the total number of singers?</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name, country
+FROM singer
+ORDER BY birthday ASC;</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>What are the names, countries for every singer in descending order of age?</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name, country
+FROM singer
+ORDER BY birthday DESC;</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id of all French singers?</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id), MIN(id), MAX(id)
+FROM singer
+WHERE country = 'France';</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id for French singers?</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id), MIN(id), MAX(id)
+FROM singer
+WHERE country = 'France';</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Show the name and the release year of the song by the youngest singer.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>sql
+-- The query cannot be answered with the given database schema.
+-- The 'singer' table does not contain information about songs or their release years.
+-- To answer this query, a 'song' table with columns like 'title', 'release_year', and 'singer_id' would be needed.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>What are the names and release years for all the songs of the youngest singer?</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name
+FROM singer
+ORDER BY birthday DESC
+LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>What are all distinct countries where singers born in 2001 are from?</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like '2001%'</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country
+FROM singer
+WHERE STRFTIME('%Y', birthday) = '2001';</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>What are  the different countries with singers born in 2001?</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country
+FROM singer
+WHERE STRFTIME('%Y', birthday) = '2001';</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>How many singers do we have?</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM singer;</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0.888</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>What is the total number of singers?</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) FROM singer;</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name, country 
+FROM singer 
+ORDER BY DATEDIFF(CURRENT_DATE, birthday) ASC;</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>What are the names, countries for every singer in descending order of age?</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name, country 
+FROM singer 
+ORDER BY DATE_PART('year', CURRENT_DATE - birthday) DESC;</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id of all French singers?</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id), MIN(id), MAX(id) 
+FROM singer 
+WHERE country = 'France';</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id for French singers?</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id), MIN(id), MAX(id) 
+FROM singer 
+WHERE country = 'France';</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="4" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Show the name and the release year of the song by the youngest singer.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>SELECT s.name, 'unknown' AS release_year
+FROM singer s
+ORDER BY s.birthday ASC
+LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>What are the names and release years for all the songs of the youngest singer?</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>SELECT s.name, NULL AS release_year FROM singer s WHERE s.birthday = (SELECT MIN(birthday) FROM singer);</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>What are all distinct countries where singers born in 2001 are from?</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like '2001%'</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>What are  the different countries with singers born in 2001?</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>How many singers do we have?</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(id) FROM singer;</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>What is the total number of singers?</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(id) FROM singer;</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name, country 
+FROM singer 
+ORDER BY birthday DESC;</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>What are the names, countries for every singer in descending order of age?</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name, country
+FROM singer
+ORDER BY birthday ASC;</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.9580000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id of all French singers?</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id) AS average\_id, MIN(id) AS min\_id, MAX(id) AS max\_id
+FROM singer
+WHERE country = 'France';</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id for French singers?</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id) AS average\_id, MIN(id) AS minimum\_id, MAX(id) AS maximum\_id
+FROM singer
+WHERE country IN ('France', 'French');</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Show the name and the release year of the song by the youngest singer.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>SELECT min(birthday) AS min_birthday
+    FROM singer
+)
+SELECT name
+FROM singer
+JOIN youngest_singer ON singer.birthday = youngest_singer.min_birthday;</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>0.458</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>What are the names and release years for all the songs of the youngest singer?</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name, MIN(birthday) AS "youngest_singer_birthday"
+FROM singer
+GROUP BY name
+HAVING MIN(birthday) = (SELECT MIN(birthday) FROM singer);</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>What are all distinct countries where singers born in 2001 are from?</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like '2001%'</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country
+FROM singer
+WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>What are  the different countries with singers born in 2001?</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country
+FROM singer
+WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1213,7 +3592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1265,26 +3644,126 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>groq_llama3</t>
+          <t>gemini_flash</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.493</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>groq_llama3</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.367</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.7458</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1.653</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ollama_llama3</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>12.369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.6415999999999999</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1.965</v>
       </c>
     </row>
   </sheetData>
@@ -1298,7 +3777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1359,6 +3838,336 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>How many singers do we have?</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>What is the total number of singers?</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>What are the names, countries for every singer in descending order of age?</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.9580000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id of all French singers?</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id for French singers?</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Show the name and the release year of the song by the youngest singer.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.458</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>What are the names and release years for all the songs of the youngest singer?</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>What are all distinct countries where singers born in 2001 are from?</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>What are  the different countries with singers born in 2001?</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/evals/reports/benchmark.xlsx
+++ b/evals/reports/benchmark.xlsx
@@ -1011,8 +1011,8 @@
         <is>
           <t>SELECT name 
 FROM singer 
-ORDER BY birthday DESC 
-LIMIT 1</t>
+WHERE birthday = (SELECT MAX(birthday) FROM singer)
+```</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -1039,17 +1039,17 @@
         <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.315</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="10">
@@ -1428,7 +1428,7 @@
         <is>
           <t>SELECT AVG(id) AS average\_id, MIN(id) AS min\_id, MAX(id) AS max\_id
 FROM singer
-WHERE country = 'France' OR country = 'French';</t>
+WHERE country = 'France';</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -1486,14 +1486,9 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>SELECT
-    AVG(id) AS average_id,
-    MIN(id) AS minimum_id,
-    MAX(id) AS maximum_id
-FROM
-    singer
-WHERE
-    country = 'France' OR country = 'French';</t>
+          <t>SELECT AVG(id) AS average\_id, MIN(id) AS minimum\_id, MAX(id) AS maximum\_id
+FROM singer
+WHERE country IN ('France', 'French');</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1520,17 +1515,17 @@
         <v>1</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.315</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="18">
@@ -1551,9 +1546,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SELECT name, MIN(birthday) AS "release year of the song"
+          <t>SELECT min(birthday) AS min_birthday
+    FROM singer
+)
+SELECT name
 FROM singer
-GROUP BY name;</t>
+JOIN young_singer ON singer.birthday = young_singer.min_birthday;</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1580,17 +1578,17 @@
         <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.315</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="19">
@@ -1611,10 +1609,10 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>SELECT name, MIN(birthday) as "youngest_singer_birthday"
+          <t>SELECT name, MIN(birthday) AS youngest_birthday
 FROM singer
 GROUP BY name
-ORDER BY youngest_singer_birthday ASC
+ORDER BY youngest_birthday ASC
 LIMIT 1;</t>
         </is>
       </c>
@@ -1675,7 +1673,7 @@
         <is>
           <t>SELECT DISTINCT country
 FROM singer
-WHERE birthday = 2001;</t>
+WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1702,17 +1700,17 @@
         <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="M20" s="2" t="n"/>
       <c r="N20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0.315</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="21">
@@ -1848,13 +1846,13 @@
         <v>0.6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.597</v>
+        <v>0.579</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -1873,13 +1871,13 @@
         <v>0.3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0</v>

--- a/evals/reports/benchmark.xlsx
+++ b/evals/reports/benchmark.xlsx
@@ -948,7 +948,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SELECT name, EXTRACT(YEAR FROM birthday) 
+          <t>SELECT name, STRFTIME('%Y', birthday) 
 FROM singer 
 ORDER BY birthday DESC 
 LIMIT 1</t>
@@ -978,17 +978,17 @@
         <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.135</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="9">
@@ -1306,8 +1306,8 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SELECT name, country 
-FROM singer 
+          <t>SELECT name, country
+FROM singer
 ORDER BY birthday DESC;</t>
         </is>
       </c>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SELECT AVG(id) AS average\_id, MIN(id) AS min\_id, MAX(id) AS max\_id
+          <t>SELECT AVG(id) AS average_id, MIN(id) AS min_id, MAX(id) AS max_id
 FROM singer
 WHERE country = 'France';</t>
         </is>
@@ -1455,17 +1455,17 @@
         <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.135</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="17">
@@ -1486,9 +1486,14 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>SELECT AVG(id) AS average\_id, MIN(id) AS minimum\_id, MAX(id) AS maximum\_id
-FROM singer
-WHERE country IN ('France', 'French');</t>
+          <t>SELECT
+    AVG(id) AS average_id,
+    MIN(id) AS minimum_id,
+    MAX(id) AS maximum_id
+FROM
+    singer
+WHERE
+    country IN ('France', 'French');</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1515,17 +1520,17 @@
         <v>1</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>0.135</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="18">
@@ -1546,12 +1551,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SELECT min(birthday) AS min_birthday
+          <t>SELECT name
+FROM singer
+JOIN (
+    SELECT MIN(birthday) AS min_birthday
     FROM singer
-)
-SELECT name
-FROM singer
-JOIN young_singer ON singer.birthday = young_singer.min_birthday;</t>
+) AS young_singer ON singer.birthday = young_singer.min_birthday;</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -1578,17 +1583,17 @@
         <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.135</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="19">
@@ -1609,11 +1614,9 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>SELECT name, MIN(birthday) AS youngest_birthday
+          <t>SELECT name, birthday
 FROM singer
-GROUP BY name
-ORDER BY youngest_birthday ASC
-LIMIT 1;</t>
+WHERE id = (SELECT MIN(id) FROM singer);</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -1846,13 +1849,13 @@
         <v>0.6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.579</v>
+        <v>0.597</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -1871,13 +1874,13 @@
         <v>0.3</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.375</v>
+        <v>0.429</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>0</v>

--- a/evals/reports/benchmark.xlsx
+++ b/evals/reports/benchmark.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -888,8 +888,8 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SELECT AVG(id) AS average_id, MIN(id) AS min_id, MAX(id) AS max_id
-FROM singer
+          <t>SELECT AVG(id), MIN(id), MAX(id) 
+FROM singer 
 WHERE country = 'France'</t>
         </is>
       </c>
@@ -1132,17 +1132,17 @@
         <is>
           <t>SELECT DISTINCT country 
 FROM singer 
-WHERE birthday LIKE '2001%'</t>
+WHERE birthday BETWEEN '2001-01-01' AND '2001-12-31'</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>1</v>
@@ -1170,610 +1170,6 @@
       </c>
       <c r="P11" s="3" t="n">
         <v>0.8149999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>How many singers do we have?</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>SELECT count(*) FROM singer</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(id) FROM singer;</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>What is the total number of singers?</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>SELECT count(*) FROM singer</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(id) FROM singer;</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>SELECT name, country
-FROM singer
-ORDER BY birthday DESC;</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>0.315</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>What are the names, countries for every singer in descending order of age?</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>SELECT name, country
-FROM singer
-ORDER BY birthday ASC;</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>What is the average, minimum, and maximum id of all French singers?</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>SELECT AVG(id) AS average_id, MIN(id) AS min_id, MAX(id) AS max_id
-FROM singer
-WHERE country = 'France';</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v>0.315</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>What is the average, minimum, and maximum id for French singers?</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>SELECT
-    AVG(id) AS average_id,
-    MIN(id) AS minimum_id,
-    MAX(id) AS maximum_id
-FROM
-    singer
-WHERE
-    country IN ('France', 'French');</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>0.315</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Show the name and the release year of the song by the youngest singer.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>SELECT name
-FROM singer
-JOIN (
-    SELECT MIN(birthday) AS min_birthday
-    FROM singer
-) AS young_singer ON singer.birthday = young_singer.min_birthday;</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>0.315</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>What are the names and release years for all the songs of the youngest singer?</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>SELECT name, birthday
-FROM singer
-WHERE id = (SELECT MIN(id) FROM singer);</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0.315</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>What are all distinct countries where singers born in 2001 are from?</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>SELECT DISTINCT country FROM singer WHERE birthday  like '2001%'</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>SELECT DISTINCT country
-FROM singer
-WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v>0.135</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>What are  the different countries with singers born in 2001?</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>SELECT DISTINCT country
-FROM singer
-WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v>0.135</v>
       </c>
     </row>
   </sheetData>
@@ -1787,7 +1183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1858,31 +1254,6 @@
         <v>0.597</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>multi_agent_groq_openrouter</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="G3" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/evals/reports/benchmark.xlsx
+++ b/evals/reports/benchmark.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -888,8 +888,8 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SELECT AVG(id), MIN(id), MAX(id) 
-FROM singer 
+          <t>SELECT AVG(id) AS average_id, MIN(id) AS min_id, MAX(id) AS max_id
+FROM singer
 WHERE country = 'France'</t>
         </is>
       </c>
@@ -1011,8 +1011,8 @@
         <is>
           <t>SELECT name 
 FROM singer 
-WHERE birthday = (SELECT MAX(birthday) FROM singer)
-```</t>
+ORDER BY birthday DESC 
+LIMIT 1</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -1039,17 +1039,17 @@
         <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.135</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="10">
@@ -1069,80 +1069,80 @@
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country 
+FROM singer 
+WHERE birthday BETWEEN '2001-01-01' AND '2001-12-31'</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>groq_llama3</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>What are  the different countries with singers born in 2001?</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>SELECT DISTINCT country 
 FROM singer 
 WHERE birthday LIKE '2001%'</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>single_agent</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>groq_llama3</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>What are  the different countries with singers born in 2001?</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>SELECT DISTINCT country 
-FROM singer 
-WHERE birthday BETWEEN '2001-01-01' AND '2001-12-31'</t>
-        </is>
-      </c>
       <c r="E11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>1</v>
@@ -1170,6 +1170,1204 @@
       </c>
       <c r="P11" s="3" t="n">
         <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>How many singers do we have?</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>What is the total number of singers?</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name, country
+FROM singer
+ORDER BY birthday ASC;</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>What are the names, countries for every singer in descending order of age?</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name, country
+FROM singer
+ORDER BY birthday DESC;</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id of all French singers?</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id), MIN(id), MAX(id)
+FROM singer
+WHERE country = 'France';</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id for French singers?</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id), MIN(id), MAX(id)
+FROM singer
+WHERE country = 'France';</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Show the name and the release year of the song by the youngest singer.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-- The query cannot be answered with the given database schema.
+-- The 'singer' table does not contain information about songs or their release years.
+-- To answer this query, a 'song' table with columns like 'title', 'release_year', and 'singer_id' would be needed.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>What are the names and release years for all the songs of the youngest singer?</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>-- The query cannot be answered with the given database schema.
+-- The 'singer' table does not contain information about songs or their release years.
+-- To answer this query, a 'songs' table with columns like 'singer_id' and 'release_year' would be needed.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>What are all distinct countries where singers born in 2001 are from?</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like '2001%'</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country
+FROM singer
+WHERE STRFTIME('%Y', birthday) = '2001';</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>What are  the different countries with singers born in 2001?</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country
+FROM singer
+WHERE STRFTIME('%Y', birthday) = '2001';</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>How many singers do we have?</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(id) FROM singer;</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>What is the total number of singers?</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>SELECT count(*) FROM singer</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(id) FROM singer;</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Show name, country for all singers ordered by age from the oldest to the youngest.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name, country 
+FROM singer 
+ORDER BY birthday DESC;</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>What are the names, countries for every singer in descending order of age?</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name ,  country  FROM singer ORDER BY birthday ASC</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name, country
+FROM singer
+ORDER BY birthday ASC;</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id of all French singers?</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>SELECT AVG(id) AS average_id, MIN(id) AS min_id, MAX(id) AS max_id
+FROM singer
+WHERE country IN ('France', 'France');</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>What is the average, minimum, and maximum id for French singers?</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>SELECT avg(Singer_ID) ,  min(Singer_ID) ,  max(Singer_ID) FROM singer WHERE country  =  'France'</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>SELECT
+    AVG(id) AS average_id,
+    MIN(id) AS minimum_id,
+    MAX(id) AS maximum_id
+FROM
+    singer
+WHERE
+    country = 'France' OR country = 'French';</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Show the name and the release year of the song by the youngest singer.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>SELECT name, birthday
+FROM singer
+ORDER BY birthday ASC
+LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>What are the names and release years for all the songs of the youngest singer?</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SELECT song_name ,  song_release_year FROM singer ORDER BY birthday desc LIMIT 1</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>SELECT name, birthday
+FROM singer
+WHERE birthday = (SELECT MIN(birthday) FROM singer);</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0.315</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>What are all distinct countries where singers born in 2001 are from?</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like '2001%'</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country
+FROM singer
+WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0.135</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>What are  the different countries with singers born in 2001?</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country FROM singer WHERE birthday  like  '2001%'</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>SELECT DISTINCT country
+FROM singer
+WHERE EXTRACT(YEAR FROM birthday) = 2001;</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>single_agent</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0.135</v>
       </c>
     </row>
   </sheetData>
@@ -1183,7 +2381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1245,15 +2443,65 @@
         <v>0.6</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.597</v>
+        <v>0.615</v>
       </c>
       <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>openrouter_mixtral</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>multi_agent_groq_openrouter</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
